--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117841404</v>
+        <v>117841243</v>
       </c>
       <c r="B2" t="n">
-        <v>57303</v>
+        <v>90499</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613433</v>
+        <v>613311</v>
       </c>
       <c r="R2" t="n">
-        <v>7271200</v>
+        <v>7271234</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,17 +756,13 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökspår</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117841100</v>
+        <v>117841303</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>79098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2079</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613305</v>
+        <v>613355</v>
       </c>
       <c r="R3" t="n">
-        <v>7271276</v>
+        <v>7271125</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117841270</v>
+        <v>117841273</v>
       </c>
       <c r="B4" t="n">
-        <v>57287</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -982,17 +968,13 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117841408</v>
+        <v>117841270</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>57287</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,26 +1009,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1054,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613433</v>
+        <v>613327</v>
       </c>
       <c r="R5" t="n">
-        <v>7271200</v>
+        <v>7271163</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,13 +1079,17 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1117,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117841273</v>
+        <v>117841404</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>57303</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,26 +1124,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1160,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613327</v>
+        <v>613433</v>
       </c>
       <c r="R6" t="n">
-        <v>7271163</v>
+        <v>7271200</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,13 +1194,17 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökspår</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,10 +1223,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117841308</v>
+        <v>117841100</v>
       </c>
       <c r="B7" t="n">
-        <v>78217</v>
+        <v>91962</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613355</v>
+        <v>613305</v>
       </c>
       <c r="R7" t="n">
-        <v>7271125</v>
+        <v>7271276</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,10 +1329,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117841303</v>
+        <v>117841340</v>
       </c>
       <c r="B8" t="n">
-        <v>79098</v>
+        <v>90517</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1345,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613355</v>
+        <v>613416</v>
       </c>
       <c r="R8" t="n">
-        <v>7271125</v>
+        <v>7271176</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1435,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117841340</v>
+        <v>117841577</v>
       </c>
       <c r="B9" t="n">
-        <v>90517</v>
+        <v>90446</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,21 +1451,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613416</v>
+        <v>613442</v>
       </c>
       <c r="R9" t="n">
-        <v>7271176</v>
+        <v>7271193</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117841596</v>
+        <v>117841408</v>
       </c>
       <c r="B10" t="n">
-        <v>57440</v>
+        <v>78480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,35 +1557,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1593,10 +1584,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613568</v>
+        <v>613433</v>
       </c>
       <c r="R10" t="n">
-        <v>7271152</v>
+        <v>7271200</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,6 +1628,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1655,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117841577</v>
+        <v>117841596</v>
       </c>
       <c r="B11" t="n">
-        <v>90446</v>
+        <v>57440</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,26 +1663,35 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1698,10 +1699,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613442</v>
+        <v>613568</v>
       </c>
       <c r="R11" t="n">
-        <v>7271193</v>
+        <v>7271152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1742,7 +1743,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117841243</v>
+        <v>117841308</v>
       </c>
       <c r="B12" t="n">
-        <v>90499</v>
+        <v>78217</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613311</v>
+        <v>613355</v>
       </c>
       <c r="R12" t="n">
-        <v>7271234</v>
+        <v>7271125</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117841243</v>
+        <v>117841340</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>90519</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613311</v>
+        <v>613416</v>
       </c>
       <c r="R2" t="n">
-        <v>7271234</v>
+        <v>7271176</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117841303</v>
+        <v>117841404</v>
       </c>
       <c r="B3" t="n">
-        <v>79098</v>
+        <v>57304</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613355</v>
+        <v>613433</v>
       </c>
       <c r="R3" t="n">
-        <v>7271125</v>
+        <v>7271200</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,13 +867,17 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Födosökspår</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117841273</v>
+        <v>117841243</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -930,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613327</v>
+        <v>613311</v>
       </c>
       <c r="R4" t="n">
-        <v>7271163</v>
+        <v>7271234</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117841270</v>
+        <v>117841100</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>91964</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,31 +1018,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613327</v>
+        <v>613305</v>
       </c>
       <c r="R5" t="n">
-        <v>7271163</v>
+        <v>7271276</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,17 +1083,13 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117841404</v>
+        <v>117841577</v>
       </c>
       <c r="B6" t="n">
-        <v>57303</v>
+        <v>90448</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,31 +1124,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>112</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613433</v>
+        <v>613442</v>
       </c>
       <c r="R6" t="n">
-        <v>7271200</v>
+        <v>7271193</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,17 +1189,13 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökspår</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,10 +1214,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117841100</v>
+        <v>117841596</v>
       </c>
       <c r="B7" t="n">
-        <v>91962</v>
+        <v>57441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1239,26 +1230,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2079</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1266,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613305</v>
+        <v>613568</v>
       </c>
       <c r="R7" t="n">
-        <v>7271276</v>
+        <v>7271152</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1329,10 +1328,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117841340</v>
+        <v>117841408</v>
       </c>
       <c r="B8" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1345,21 +1344,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613416</v>
+        <v>613433</v>
       </c>
       <c r="R8" t="n">
-        <v>7271176</v>
+        <v>7271200</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1435,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117841577</v>
+        <v>117841303</v>
       </c>
       <c r="B9" t="n">
-        <v>90446</v>
+        <v>79100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,21 +1450,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1478,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613442</v>
+        <v>613355</v>
       </c>
       <c r="R9" t="n">
-        <v>7271193</v>
+        <v>7271125</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117841408</v>
+        <v>117841270</v>
       </c>
       <c r="B10" t="n">
-        <v>78480</v>
+        <v>57288</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1557,26 +1556,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1584,10 +1588,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613433</v>
+        <v>613327</v>
       </c>
       <c r="R10" t="n">
-        <v>7271200</v>
+        <v>7271163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1622,13 +1626,17 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1647,10 +1655,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117841596</v>
+        <v>117841308</v>
       </c>
       <c r="B11" t="n">
-        <v>57440</v>
+        <v>78219</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,35 +1671,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1699,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613568</v>
+        <v>613355</v>
       </c>
       <c r="R11" t="n">
-        <v>7271152</v>
+        <v>7271125</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1743,6 +1742,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117841308</v>
+        <v>117841273</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>78482</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,21 +1777,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613355</v>
+        <v>613327</v>
       </c>
       <c r="R12" t="n">
-        <v>7271125</v>
+        <v>7271163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2634,6 +2634,131 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>121941811</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57383</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Vindelälven, Utterbäckselet., Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>613093</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7270948</v>
+      </c>
+      <c r="S20" t="n">
+        <v>50</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Lämpligt häckningsområde för fågeln med liggande och stående döda träd, mest gran. Hackspår i barken på flera granar. Fågeln observerad i området under flera års tid, ända upp till Forsmyrtjärnen.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jan Berglund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jan Berglund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2636,7 +2636,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121941811</v>
+        <v>121941832</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2669,11 +2669,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2730,11 +2726,6 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Lämpligt häckningsområde för fågeln med liggande och stående döda träd, mest gran. Hackspår i barken på flera granar. Fågeln observerad i området under flera års tid, ända upp till Forsmyrtjärnen.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2636,7 +2636,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121941832</v>
+        <v>121941811</v>
       </c>
       <c r="B20" t="n">
         <v>57383</v>
@@ -2669,7 +2669,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -2726,6 +2730,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Lämpligt häckningsområde för fågeln med liggande och stående döda träd, mest gran. Hackspår i barken på flera granar. Fågeln observerad i området under flera års tid, ända upp till Forsmyrtjärnen.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2639,7 +2639,7 @@
         <v>121941811</v>
       </c>
       <c r="B20" t="n">
-        <v>57383</v>
+        <v>57384</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2759,6 +2759,121 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123350306</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57358</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Junnisvara., Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>613213</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7271279</v>
+      </c>
+      <c r="S21" t="n">
+        <v>100</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2015-12-17</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2015-12-17</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Förbiflygande vid Junnisvara.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jan Berglund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jan Berglund</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>123350306</v>
       </c>
       <c r="B21" t="n">
-        <v>57358</v>
+        <v>57361</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>123350306</v>
       </c>
       <c r="B21" t="n">
-        <v>57361</v>
+        <v>57367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>123350306</v>
       </c>
       <c r="B21" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2764,7 +2764,7 @@
         <v>123350306</v>
       </c>
       <c r="B21" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 21437-2024 artfynd.xlsx
+++ b/artfynd/A 21437-2024 artfynd.xlsx
@@ -2815,7 +2815,7 @@
         <v>7271279</v>
       </c>
       <c r="S21" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
